--- a/generation_zy/Materials-stack4列.xlsx
+++ b/generation_zy/Materials-stack4列.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="390" yWindow="390" windowWidth="21555" windowHeight="10635" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="PlateStack" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -31,13 +31,13 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
@@ -56,165 +56,25 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -241,198 +101,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
         <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -499,256 +173,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -757,7 +189,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -781,79 +212,149 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
     </dxf>
@@ -910,149 +411,32 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1378,6 +762,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1388,50 +773,50 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
-    <col width="33.7142857142857" customWidth="1" style="5" min="2" max="2"/>
-    <col width="21.2857142857143" customWidth="1" style="5" min="3" max="3"/>
-    <col width="22.2857142857143" customWidth="1" style="5" min="4" max="4"/>
-    <col width="21.7142857142857" customWidth="1" style="5" min="5" max="5"/>
-    <col width="15.2857142857143" customWidth="1" style="5" min="6" max="8"/>
-    <col width="15.4285714285714" customWidth="1" style="5" min="9" max="9"/>
-    <col width="26.8571428571429" customWidth="1" style="5" min="10" max="10"/>
-    <col width="12.5714285714286" customWidth="1" style="5" min="11" max="11"/>
-    <col width="12.4285714285714" customWidth="1" style="5" min="12" max="12"/>
-    <col width="17.5714285714286" customWidth="1" style="5" min="13" max="13"/>
-    <col width="14.2857142857143" customWidth="1" style="5" min="14" max="14"/>
+    <col width="33.7109375" customWidth="1" style="4" min="2" max="2"/>
+    <col width="21.28515625" customWidth="1" style="4" min="3" max="3"/>
+    <col width="22.28515625" customWidth="1" style="4" min="4" max="4"/>
+    <col width="21.7109375" customWidth="1" style="4" min="5" max="5"/>
+    <col width="15.28515625" customWidth="1" style="4" min="6" max="8"/>
+    <col width="15.42578125" customWidth="1" style="4" min="9" max="9"/>
+    <col width="26.85546875" customWidth="1" style="4" min="10" max="10"/>
+    <col width="12.5703125" customWidth="1" style="4" min="11" max="11"/>
+    <col width="12.42578125" customWidth="1" style="4" min="12" max="12"/>
+    <col width="17.5703125" customWidth="1" style="4" min="13" max="13"/>
+    <col width="14.28515625" customWidth="1" style="4" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>A列</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>B列</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>C列</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>规格设置</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="5">
-      <c r="A2" s="3" t="n">
+    <row r="2" ht="16.5" customHeight="1" s="4">
+      <c r="A2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -1456,27 +841,27 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>TA1-过滤板-2A01</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>TA1-枪头_200ul-B04</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>TA1-试剂板-A03</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="13" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -1496,7 +881,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
@@ -1504,7 +889,7 @@
           <t>TA1-称量载具_900ul-1</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>TA1-枪头_1000ul-B05</t>
         </is>
@@ -1516,7 +901,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="13" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
@@ -1524,15 +909,15 @@
           <t>TA1-板盖-A01</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>TA2-试剂板-A02</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
@@ -1540,17 +925,17 @@
           <t>TA1-金属板-B01</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>TA2-试剂板-A03</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>TA2-试剂板-B02</t>
         </is>
@@ -1560,10 +945,10 @@
       <c r="J8" s="0" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>TA2-试剂板-B03</t>
         </is>
@@ -1609,7 +994,7 @@
       <c r="N13" s="0" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -1916,7 +1301,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>尾缀-XXX 代表 对应HIWO的位置</t>
         </is>
@@ -1980,94 +1365,98 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
-    <col width="13.8571428571429" customWidth="1" style="5" min="2" max="6"/>
+    <col width="13.85546875" customWidth="1" style="4" min="2" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Hopper1</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Hopper2</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Hopper3</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Hopper4</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Hopper5</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>20260924-001</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
+          <t>20260922-001</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>20261012-001</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
+      <c r="A4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C6"/>
@@ -2082,7 +1471,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -2090,24 +1479,24 @@
           <t>TA1-试剂板-A02</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>TA2-试剂板-B02</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>TA3-试剂板-A02</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>TA1-试剂板-A03</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>TA2-试剂板-B03</t>
         </is>
@@ -2119,7 +1508,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>TA1-试剂板-B02</t>
         </is>
@@ -2129,19 +1518,19 @@
           <t>TA1-封膜-产物板-2B01</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>TA1-枪头_200ul-B04</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>TA1-试剂板-B03</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TA1-过滤板-2A01</t>
         </is>
@@ -2153,7 +1542,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>TA2-试剂板-A02</t>
         </is>
@@ -2163,24 +1552,24 @@
           <t>TA1-称量载具_900ul-1</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>TA1-枪头_1000ul-B05</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>TA2-试剂板-A03</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>TA1-称量载具_8ml-2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
+      <c r="C7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2193,7 +1582,7 @@
           <t>TA1-板盖-A01</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="13" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2312,7 +1701,7 @@
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>Ic1ccccc1</t>
+          <t>N2(CCNCC2)C3=CC=CC=C3</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
@@ -2386,7 +1775,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>试剂1,cesium hydroxide</t>
+          <t>DMF</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -2460,7 +1849,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>试剂2,palladium diacetate</t>
+          <t>空</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -2534,7 +1923,7 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>溶剂1,toluene</t>
+          <t>空</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -8531,7 +7920,7 @@
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
-          <t>试剂-12</t>
+          <t>IS1</t>
         </is>
       </c>
       <c r="E112" s="0" t="inlineStr">
@@ -10316,12 +9705,12 @@
     <row r="202">
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>Nc1ccccc1</t>
+          <t>ClC1=NC=CC=N1</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>20260924-001</t>
+          <t>20260922-001</t>
         </is>
       </c>
       <c r="D202" s="0" t="inlineStr"/>
@@ -10330,6 +9719,17 @@
       </c>
     </row>
     <row r="203">
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t>K2CO3</t>
+        </is>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>20261012-001</t>
+        </is>
+      </c>
+      <c r="D203" s="0" t="inlineStr"/>
       <c r="F203" s="17" t="n">
         <v>10</v>
       </c>
@@ -10383,12 +9783,47 @@
           <t>1</t>
         </is>
       </c>
+      <c r="H212" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I212" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J212" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K212" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L212" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M212" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N212" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A201:A203"/>
     <mergeCell ref="A100:A196"/>
     <mergeCell ref="A1:A96"/>
-    <mergeCell ref="A201:A202"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10400,7 +9835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10481,36 +9916,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AgNO3</t>
+          <t>ClC1=NC=CC=N1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C6H7N</t>
+          <t>C4H3ClN2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nc1ccccc1</t>
+          <t>ClC1=NC=CC=N1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="n">
-        <v>93.13</v>
+        <v>45.84</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>1.3</v>
+        <v>0.53</v>
       </c>
       <c r="L2" t="n">
-        <v>121.07</v>
+        <v>59.59</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -10525,44 +9960,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OCc1ccc(I)cc1</t>
+          <t>N2(CCNCC2)C3=CC=CC=C3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C7H7IO</t>
+          <t>C10H14N2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OCc1ccc(I)cc1</t>
+          <t>N2(CCNCC2)C3=CC=CC=C3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H3" t="n">
-        <v>234.04</v>
+        <v>77.84</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3404</v>
+        <v>0.0389</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3</v>
+        <v>0.64</v>
       </c>
       <c r="L3" t="n">
-        <v>304.25</v>
+        <v>101.19</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="4">
@@ -10571,7 +10006,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>试剂1,cesium hydroxide</t>
+          <t>K2CO3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -10579,28 +10014,26 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>88.48</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>115.02</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -10609,7 +10042,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>试剂2,palladium diacetate</t>
+          <t>DMF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -10617,65 +10050,27 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>溶剂1,toluene</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
